--- a/figures/Table_studies_per_country.xlsx
+++ b/figures/Table_studies_per_country.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
-  <si>
-    <t>Country_or_Region</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+  <si>
+    <t>Geo_general</t>
   </si>
   <si>
     <t>Count</t>
@@ -110,151 +110,94 @@
     <t>30</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>40</t>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>In silico</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global </t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>USA</t>
   </si>
   <si>
     <t>Brazil</t>
   </si>
   <si>
-    <t>Neotropical</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>Costa Rica</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>Colombia</t>
-  </si>
-  <si>
-    <t>Global</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>Panama</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Belize</t>
-  </si>
-  <si>
-    <t>Brazil and Bolivia and Paraguay</t>
-  </si>
-  <si>
-    <t>Egypt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global </t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Israel</t>
-  </si>
-  <si>
-    <t>Malaysia</t>
-  </si>
-  <si>
-    <t>Peru</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Bahamas and Greater Antilles and Lesser Antilles</t>
-  </si>
-  <si>
-    <t>Bolivia</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>Colombia and Venezuela</t>
-  </si>
-  <si>
-    <t>Costa Rica and Panama</t>
-  </si>
-  <si>
-    <t>Cuba</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Neotropics and Europe</t>
-  </si>
-  <si>
-    <t>Netherlands and Belgium and Hungary and Romania</t>
-  </si>
-  <si>
-    <t>North Africa</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>Romania and Hungary</t>
-  </si>
-  <si>
-    <t>Ucrane and Russia and Azerbaijan</t>
+    <t>Multicountry</t>
   </si>
 </sst>
 </file>
@@ -316,10 +259,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>22.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -327,10 +270,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -338,10 +281,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -349,10 +292,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
@@ -360,10 +303,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
@@ -371,10 +314,10 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C7" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
@@ -382,10 +325,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="9">
@@ -393,10 +336,10 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="10">
@@ -404,10 +347,10 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
@@ -415,21 +358,21 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="e">
-        <v>#N/A</v>
+      <c r="B12" t="s">
+        <v>42</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
@@ -437,10 +380,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="14">
@@ -448,7 +391,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
         <v>2.0</v>
@@ -459,7 +402,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C15" t="n">
         <v>2.0</v>
@@ -470,7 +413,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C16" t="n">
         <v>2.0</v>
@@ -481,7 +424,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C17" t="n">
         <v>2.0</v>
@@ -492,7 +435,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C18" t="n">
         <v>2.0</v>
@@ -503,7 +446,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C19" t="n">
         <v>2.0</v>
@@ -514,7 +457,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C20" t="n">
         <v>2.0</v>
@@ -525,7 +468,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n">
         <v>2.0</v>
@@ -536,10 +479,10 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C22" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="23">
@@ -547,10 +490,10 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C23" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="24">
@@ -558,10 +501,10 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="25">
@@ -569,10 +512,10 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="26">
@@ -580,10 +523,10 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="27">
@@ -591,10 +534,10 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="28">
@@ -602,10 +545,10 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C28" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="29">
@@ -613,10 +556,10 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C29" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="30">
@@ -624,10 +567,10 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C30" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="31">
@@ -635,120 +578,10 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
     </row>
   </sheetData>

--- a/figures/Table_studies_per_country.xlsx
+++ b/figures/Table_studies_per_country.xlsx
@@ -179,16 +179,16 @@
     <t>Germany</t>
   </si>
   <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
     <t>Colombia</t>
   </si>
   <si>
-    <t>Costa Rica</t>
+    <t>Mexico</t>
   </si>
   <si>
     <t>Global</t>
-  </si>
-  <si>
-    <t>Mexico</t>
   </si>
   <si>
     <t>USA</t>
@@ -515,7 +515,7 @@
         <v>55</v>
       </c>
       <c r="C25" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="26">
@@ -526,7 +526,7 @@
         <v>56</v>
       </c>
       <c r="C26" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="27">
@@ -537,7 +537,7 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="28">
@@ -570,7 +570,7 @@
         <v>60</v>
       </c>
       <c r="C30" t="n">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="31">
@@ -581,7 +581,7 @@
         <v>61</v>
       </c>
       <c r="C31" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
     </row>
   </sheetData>

--- a/figures/Table_studies_per_country.xlsx
+++ b/figures/Table_studies_per_country.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Geo_general</t>
   </si>
@@ -110,6 +110,9 @@
     <t>30</t>
   </si>
   <si>
+    <t>31</t>
+  </si>
+  <si>
     <t>Bolivia</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
     <t>Italy</t>
   </si>
   <si>
+    <t>North Africa</t>
+  </si>
+  <si>
     <t>Portugal</t>
   </si>
   <si>
@@ -179,13 +185,13 @@
     <t>Germany</t>
   </si>
   <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
     <t>Costa Rica</t>
-  </si>
-  <si>
-    <t>Colombia</t>
-  </si>
-  <si>
-    <t>Mexico</t>
   </si>
   <si>
     <t>Global</t>
@@ -259,7 +265,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>1.0</v>
@@ -270,7 +276,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
         <v>1.0</v>
@@ -281,7 +287,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
         <v>1.0</v>
@@ -292,7 +298,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
         <v>1.0</v>
@@ -303,7 +309,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n">
         <v>1.0</v>
@@ -314,7 +320,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
         <v>1.0</v>
@@ -325,7 +331,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
         <v>1.0</v>
@@ -336,7 +342,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
         <v>1.0</v>
@@ -347,7 +353,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
         <v>1.0</v>
@@ -358,7 +364,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>1.0</v>
@@ -369,7 +375,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="n">
         <v>1.0</v>
@@ -380,7 +386,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
         <v>1.0</v>
@@ -391,10 +397,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="15">
@@ -402,7 +408,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n">
         <v>2.0</v>
@@ -413,7 +419,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" t="n">
         <v>2.0</v>
@@ -424,7 +430,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="n">
         <v>2.0</v>
@@ -435,7 +441,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" t="n">
         <v>2.0</v>
@@ -446,7 +452,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="n">
         <v>2.0</v>
@@ -457,7 +463,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="n">
         <v>2.0</v>
@@ -468,7 +474,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" t="n">
         <v>2.0</v>
@@ -479,10 +485,10 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="23">
@@ -490,10 +496,10 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="24">
@@ -501,7 +507,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" t="n">
         <v>5.0</v>
@@ -512,10 +518,10 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C25" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="26">
@@ -523,7 +529,7 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26" t="n">
         <v>8.0</v>
@@ -534,7 +540,7 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" t="n">
         <v>8.0</v>
@@ -545,7 +551,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C28" t="n">
         <v>9.0</v>
@@ -556,10 +562,10 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" t="n">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="30">
@@ -567,10 +573,10 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C30" t="n">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="31">
@@ -578,9 +584,20 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" t="n">
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" t="n">
         <v>24.0</v>
       </c>
     </row>
